--- a/data/trending_integrated_20261023_10.xlsx
+++ b/data/trending_integrated_20261023_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4160</v>
+        <v>4190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+10.93%</t>
+          <t>'+11.73%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>96017140788</v>
+        <v>100177794262</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 도발 관련 방산주 상승 기대감 및 미 증시 폭락 속 록히드마틴 급등 영향. 외인 매도 및 주가 조작 의혹 제기.</t>
+          <t>북한 관련 이슈 및 미군 특수 정찰기 포착 등으로 인한 방산주 상승 기대감. 객관적 분석 부족.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['북한 도발', '방산주', '록히드마틴']</t>
+          <t>['방산주', '북한']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60400</v>
+        <v>60800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.03%</t>
+          <t>'+9.75%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="F3" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G3" t="n">
-        <v>581</v>
+        <v>617</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -693,7 +693,7 @@
         <v>56300</v>
       </c>
       <c r="L3" t="n">
-        <v>60700</v>
+        <v>60900</v>
       </c>
       <c r="M3" t="n">
         <v>56200</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>388152787100</v>
+        <v>415754141750</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1228000</v>
+        <v>14600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>545</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>1313</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>48.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1223000</v>
+        <v>14530</v>
       </c>
       <c r="K4" t="n">
-        <v>1200000</v>
+        <v>14190</v>
       </c>
       <c r="L4" t="n">
-        <v>1229000</v>
+        <v>14610</v>
       </c>
       <c r="M4" t="n">
-        <v>1171000</v>
+        <v>13810</v>
       </c>
       <c r="N4" t="n">
-        <v>48.79</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1351975006500</v>
+        <v>11860662630</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q4" t="n">
-        <v>468000</v>
+        <v>3320</v>
       </c>
       <c r="R4" t="n">
-        <v>-272000</v>
+        <v>-17000</v>
       </c>
       <c r="S4" t="n">
-        <v>79000</v>
+        <v>27000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 관련 논란 및 국민연금 운용에 대한 불만 제기. IPO 중단 시기 놓친 점 언급.</t>
+          <t>주가 조작 및 정치적 이슈에 대한 불만 제기가 다수. 객관적인 기업 분석이나 전망은 없음.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['솔리다임', 'IPO', '국민연금']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8680</v>
+        <v>8700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H5" t="n">
         <v>5.11</v>
@@ -880,13 +880,13 @@
         <v>9460</v>
       </c>
       <c r="M5" t="n">
-        <v>8670</v>
+        <v>8640</v>
       </c>
       <c r="N5" t="n">
         <v>5.15</v>
       </c>
       <c r="O5" t="n">
-        <v>4899764635</v>
+        <v>5147023755</v>
       </c>
       <c r="P5" t="n">
         <v>15900</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>전 세계 특허 획득 및 3상 성공 가능성에도 불구하고 약효 증명 부족으로 인한 주가 하락. 주포 장난질 및 허풍제약 비판.</t>
+          <t>뇌졸증 치료제 관련 허위 정보 및 단기 매매 의혹 제기. 주가 조작 및 먹튀 비판. AI 시대 제약 바이오의 중요성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['특허 획득', '3상 성공', '약효 증명']</t>
+          <t>['뇌졸증 치료제', '단주 거래', '먹튀']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13250</v>
+        <v>1223000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>530</v>
       </c>
       <c r="G6" t="n">
-        <v>143</v>
+        <v>1396</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>48.77</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13340</v>
+        <v>1223000</v>
       </c>
       <c r="K6" t="n">
-        <v>12840</v>
+        <v>1200000</v>
       </c>
       <c r="L6" t="n">
-        <v>13310</v>
+        <v>1235000</v>
       </c>
       <c r="M6" t="n">
-        <v>12530</v>
+        <v>1171000</v>
       </c>
       <c r="N6" t="n">
-        <v>3.48</v>
+        <v>48.79</v>
       </c>
       <c r="O6" t="n">
-        <v>23058437880</v>
+        <v>1559186327000</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>1640</v>
+        <v>468000</v>
       </c>
       <c r="R6" t="n">
-        <v>127000</v>
+        <v>-272000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신주 폭락 영향으로 인한 주가 하락 우려. 기판 개발 특허 등록 소식 있으나 전반적으로 부정적.</t>
+          <t>솔리다임 상장 이슈와 관련한 긍정적 기대감 있으나, 객관적 근거 제시 부족. 일부 정치적 발언 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신주', '폭락', '기판 개발']</t>
+          <t>['솔리다임']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7150</v>
+        <v>7190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.11%</t>
+          <t>'-0.55%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H7" t="n">
         <v>25.42</v>
@@ -1061,7 +1061,7 @@
         <v>7100</v>
       </c>
       <c r="L7" t="n">
-        <v>7190</v>
+        <v>7210</v>
       </c>
       <c r="M7" t="n">
         <v>7010</v>
@@ -1070,7 +1070,7 @@
         <v>25.47</v>
       </c>
       <c r="O7" t="n">
-        <v>5255616955</v>
+        <v>5806950875</v>
       </c>
       <c r="P7" t="n">
         <v>17950</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>분기 순이익 7,556억 달성으로 재무 상태 급격히 개선. FLiPP 개발 성공 및 중장기적 주가 재평가 기대.</t>
+          <t>분기 순이익 증가 및 재무 상태 개선 등 긍정적인 실적 발표. FLiPP 개발 성공에 대한 기대감 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['분기 순이익', 'FLiPP', '재무 상태']</t>
+          <t>['순이익', 'FLiPP']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>210250</v>
+        <v>13240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.98%</t>
+          <t>'-0.75%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>550</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>1617</v>
+        <v>153</v>
       </c>
       <c r="H8" t="n">
-        <v>46.13</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>214500</v>
+        <v>13340</v>
       </c>
       <c r="K8" t="n">
-        <v>206000</v>
+        <v>12840</v>
       </c>
       <c r="L8" t="n">
-        <v>210500</v>
+        <v>13310</v>
       </c>
       <c r="M8" t="n">
-        <v>203500</v>
+        <v>12530</v>
       </c>
       <c r="N8" t="n">
-        <v>46.14</v>
+        <v>3.48</v>
       </c>
       <c r="O8" t="n">
-        <v>1038424143250</v>
+        <v>25132516270</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>1640</v>
       </c>
       <c r="R8" t="n">
-        <v>-319000</v>
+        <v>127000</v>
       </c>
       <c r="S8" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 이슈 관련 부정적 언급 다수. 주가 반등에 대한 회의적인 시각 존재.</t>
+          <t>미국 광통신 주가 폭락에 따른 국내 주가 하락 우려. 일부 긍정적 정보(기판개발 특허) 언급되나 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['정치', '주가 반등', '개미 꼬심']</t>
+          <t>['광통신']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16690</v>
+        <v>17090</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.64%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H9" t="n">
-        <v>27.89</v>
+        <v>3.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17320</v>
+        <v>17350</v>
       </c>
       <c r="K9" t="n">
-        <v>16810</v>
+        <v>18130</v>
       </c>
       <c r="L9" t="n">
-        <v>16850</v>
+        <v>19070</v>
       </c>
       <c r="M9" t="n">
-        <v>16450</v>
+        <v>16530</v>
       </c>
       <c r="N9" t="n">
-        <v>27.87</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>10967242580</v>
+        <v>41771215770</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>16450</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-46000</v>
+        <v>-40000</v>
       </c>
       <c r="S9" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신저점 갱신 및 주주환원 정책 발표 가능성 언급. 조선업 부진 및 최악의 종목이라는 부정적 평가 존재.</t>
+          <t>보안주에 대한 관심 증가 및 AI 에이전트 해킹 이슈로 인한 기대감. 주가 조작 의혹 및 부정적 의견 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['신저점', '주주환원', '조선업']</t>
+          <t>['보안주', 'AI']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59100</v>
+        <v>208750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>134</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>95</v>
+        <v>540</v>
       </c>
       <c r="G10" t="n">
-        <v>343</v>
+        <v>1596</v>
       </c>
       <c r="H10" t="n">
-        <v>22.25</v>
+        <v>46.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>61600</v>
+        <v>214500</v>
       </c>
       <c r="K10" t="n">
-        <v>59600</v>
+        <v>206000</v>
       </c>
       <c r="L10" t="n">
-        <v>60000</v>
+        <v>211000</v>
       </c>
       <c r="M10" t="n">
-        <v>57700</v>
+        <v>203500</v>
       </c>
       <c r="N10" t="n">
-        <v>22.26</v>
+        <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>42951672250</v>
+        <v>1143643513500</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-25000</v>
+        <v>-319000</v>
       </c>
       <c r="S10" t="n">
-        <v>-69000</v>
+        <v>113000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미 증시 폭락 영향 및 공매도 누적에 따른 주가 하락 우려. 정부 부재 및 국민연금 방어 실패에 대한 비판.</t>
+          <t>정치적 발언이 주를 이루며, 주가에 대한 객관적인 분석이나 근거는 부족함. 감정적인 비난이 다수.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미 증시 폭락', '공매도', '주가 하락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16600</v>
+        <v>16690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.32%</t>
+          <t>'-3.64%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.48</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
         <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H11" t="n">
-        <v>3.77</v>
+        <v>27.89</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17350</v>
+        <v>17320</v>
       </c>
       <c r="K11" t="n">
-        <v>18130</v>
+        <v>16810</v>
       </c>
       <c r="L11" t="n">
-        <v>19070</v>
+        <v>16850</v>
       </c>
       <c r="M11" t="n">
-        <v>16600</v>
+        <v>16450</v>
       </c>
       <c r="N11" t="n">
-        <v>3.29</v>
+        <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>39330113245</v>
+        <v>12274392810</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>6320</v>
+        <v>16450</v>
       </c>
       <c r="R11" t="n">
-        <v>-40000</v>
+        <v>-46000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 달리 주가 부진. 해킹 관련 이슈 및 주가 조작 의혹 제기. 매수 주의.</t>
+          <t>신저점 경신 및 주가 하락에 대한 불만이 주를 이룸. 주주 환원 정책에 대한 기대감 언급되나 불확실.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안주', '해킹', '주가 조작']</t>
+          <t>['주주환원']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,97 +1476,189 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9590</v>
+        <v>59100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.96%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.19</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="G12" t="n">
-        <v>172</v>
+        <v>359</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5</v>
+        <v>22.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10090</v>
+        <v>61600</v>
       </c>
       <c r="K12" t="n">
-        <v>9770</v>
+        <v>59600</v>
       </c>
       <c r="L12" t="n">
-        <v>10060</v>
+        <v>60000</v>
       </c>
       <c r="M12" t="n">
-        <v>9280</v>
+        <v>57700</v>
       </c>
       <c r="N12" t="n">
-        <v>3.69</v>
+        <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>24512980015</v>
+        <v>47859558350</v>
       </c>
       <c r="P12" t="n">
-        <v>11690</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>2270</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-5000</v>
+        <v>-25000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>조정 및 횡보 예상. 미국장 및 국장 하락에도 불구하고 상승 가능성 언급하나, 매도 의견도 존재.</t>
+          <t>공매도 및 시장 하락에 대한 부정적인 전망이 지배적. 일부 반등에 대한 기대도 있으나 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['공매도']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9510</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-5.75%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="E13" t="n">
+        <v>79</v>
+      </c>
+      <c r="F13" t="n">
+        <v>49</v>
+      </c>
+      <c r="G13" t="n">
+        <v>180</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>10090</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9770</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10060</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9280</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O13" t="n">
+        <v>25853517220</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>종목에 대한 부정적인 전망과 함께 야금야금 털고 있다는 의견 존재. 일부 긍정적인 기대도 있으나 불확실.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
         <v>0.2</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>['조정', '횡보', '수익 축소']</t>
-        </is>
-      </c>
-      <c r="X12" t="n">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['조정']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
         <v>6</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>396300</t>
         </is>

--- a/data/trending_integrated_20261023_10.xlsx
+++ b/data/trending_integrated_20261023_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4190</v>
+        <v>4225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+11.73%</t>
+          <t>'+12.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>100177794262</v>
+        <v>106781430196</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 이슈 및 미군 특수 정찰기 포착 등으로 인한 방산주 상승 기대감. 객관적 분석 부족.</t>
+          <t>북한 관련 지정학적 이슈 및 미국 방산주 급등 영향. 개인 투자자 매수세 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['방산주', '북한']</t>
+          <t>['북한', '방산주', '외국인']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60800</v>
+        <v>60000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.75%</t>
+          <t>'+8.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>415754141750</v>
+        <v>437062622150</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관 매수세 유입 및 자사주 매입/소각 발표에 따른 주가 상승 전망. MSCI 패시브 자금 유입 가능성 제기.</t>
+          <t>외인·기관 매수세 유입 및 자사주 매입/소각 효과 기대. MSCI 패시브 자금 유입 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI', '패시브 자금']</t>
+          <t>['외인', '자사주 매입', 'MSCI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14600</v>
+        <v>8770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F4" t="n">
         <v>41</v>
       </c>
-      <c r="F4" t="n">
-        <v>23</v>
-      </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="H4" t="n">
-        <v>9.890000000000001</v>
+        <v>5.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14530</v>
+        <v>8680</v>
       </c>
       <c r="K4" t="n">
-        <v>14190</v>
+        <v>9410</v>
       </c>
       <c r="L4" t="n">
-        <v>14610</v>
+        <v>9460</v>
       </c>
       <c r="M4" t="n">
-        <v>13810</v>
+        <v>8640</v>
       </c>
       <c r="N4" t="n">
-        <v>9.949999999999999</v>
+        <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>11860662630</v>
+        <v>5228684085</v>
       </c>
       <c r="P4" t="n">
-        <v>40350</v>
+        <v>15900</v>
       </c>
       <c r="Q4" t="n">
-        <v>3320</v>
+        <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>-17000</v>
+        <v>-186000</v>
       </c>
       <c r="S4" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주가 조작 및 정치적 이슈에 대한 불만 제기가 다수. 객관적인 기업 분석이나 전망은 없음.</t>
+          <t>신풍제약 관련하여 뇌졸중 치료제, 에볼라 치료제 관련 내용 및 특허 언급. 허풍제약이라는 비판적 의견과 함께 단타 매매 및 주포 장난질 의혹 제기. 긍정적 소식에도 불구하고 부정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['뇌졸중 치료제', '에볼라', '특허']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8700</v>
+        <v>14510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="H5" t="n">
-        <v>5.11</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8680</v>
+        <v>14530</v>
       </c>
       <c r="K5" t="n">
-        <v>9410</v>
+        <v>14190</v>
       </c>
       <c r="L5" t="n">
-        <v>9460</v>
+        <v>14610</v>
       </c>
       <c r="M5" t="n">
-        <v>8640</v>
+        <v>13810</v>
       </c>
       <c r="N5" t="n">
-        <v>5.15</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>5147023755</v>
+        <v>13920064960</v>
       </c>
       <c r="P5" t="n">
-        <v>15900</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>6310</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>-186000</v>
+        <v>-17000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>뇌졸증 치료제 관련 허위 정보 및 단기 매매 의혹 제기. 주가 조작 및 먹튀 비판. AI 시대 제약 바이오의 중요성 언급.</t>
+          <t>정치적 비난 다수. 주가조작 및 공매도 관련 의혹 제기. 실적 관련 언급 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['뇌졸증 치료제', '단주 거래', '먹튀']</t>
+          <t>['주가조작', '공매도', '외인보유률']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1223000</v>
+        <v>1221000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="G6" t="n">
-        <v>1396</v>
+        <v>1417</v>
       </c>
       <c r="H6" t="n">
         <v>48.77</v>
@@ -978,7 +978,7 @@
         <v>48.79</v>
       </c>
       <c r="O6" t="n">
-        <v>1559186327000</v>
+        <v>1667626834500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>솔리다임 상장 이슈와 관련한 긍정적 기대감 있으나, 객관적 근거 제시 부족. 일부 정치적 발언 혼재.</t>
+          <t>목표가 상향 제시 및 기관 매수 방어 움직임. 솔리다임 이슈 완화 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['솔리다임']</t>
+          <t>['목표가', '기관 매수', '솔리다임']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7190</v>
+        <v>13225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.55%</t>
+          <t>'-0.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>215</v>
+        <v>158</v>
       </c>
       <c r="H7" t="n">
-        <v>25.42</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7230</v>
+        <v>13340</v>
       </c>
       <c r="K7" t="n">
-        <v>7100</v>
+        <v>12840</v>
       </c>
       <c r="L7" t="n">
-        <v>7210</v>
+        <v>13310</v>
       </c>
       <c r="M7" t="n">
-        <v>7010</v>
+        <v>12530</v>
       </c>
       <c r="N7" t="n">
-        <v>25.47</v>
+        <v>3.48</v>
       </c>
       <c r="O7" t="n">
-        <v>5806950875</v>
+        <v>27445961110</v>
       </c>
       <c r="P7" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>7010</v>
+        <v>1640</v>
       </c>
       <c r="R7" t="n">
-        <v>12000</v>
+        <v>127000</v>
       </c>
       <c r="S7" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>분기 순이익 증가 및 재무 상태 개선 등 긍정적인 실적 발표. FLiPP 개발 성공에 대한 기대감 존재.</t>
+          <t>미국 광통신주 급락 영향 및 국내 증시 하방 압력. EUV 반도체 유리기판 특허 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['순이익', 'FLiPP']</t>
+          <t>['광통신', 'EUV', '유리기판']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13240</v>
+        <v>7160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-0.97%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
         <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>25.42</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13340</v>
+        <v>7230</v>
       </c>
       <c r="K8" t="n">
-        <v>12840</v>
+        <v>7100</v>
       </c>
       <c r="L8" t="n">
-        <v>13310</v>
+        <v>7210</v>
       </c>
       <c r="M8" t="n">
-        <v>12530</v>
+        <v>7010</v>
       </c>
       <c r="N8" t="n">
-        <v>3.48</v>
+        <v>25.47</v>
       </c>
       <c r="O8" t="n">
-        <v>25132516270</v>
+        <v>6353181855</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q8" t="n">
-        <v>1640</v>
+        <v>7010</v>
       </c>
       <c r="R8" t="n">
-        <v>127000</v>
+        <v>12000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 폭락에 따른 국내 주가 하락 우려. 일부 긍정적 정보(기판개발 특허) 언급되나 부정적 전망 우세.</t>
+          <t>분기 순이익 증가 및 재무 상태 개선 등 긍정적인 실적 발표. FLiPP 개발 성공에 대한 기대감 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신']</t>
+          <t>['순이익', 'FLiPP']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17090</v>
+        <v>209500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-2.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>536</v>
       </c>
       <c r="G9" t="n">
-        <v>113</v>
+        <v>1551</v>
       </c>
       <c r="H9" t="n">
-        <v>3.77</v>
+        <v>46.13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17350</v>
+        <v>214500</v>
       </c>
       <c r="K9" t="n">
-        <v>18130</v>
+        <v>206000</v>
       </c>
       <c r="L9" t="n">
-        <v>19070</v>
+        <v>211000</v>
       </c>
       <c r="M9" t="n">
-        <v>16530</v>
+        <v>203500</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>41771215770</v>
+        <v>1202258655750</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-40000</v>
+        <v>-319000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>보안주에 대한 관심 증가 및 AI 에이전트 해킹 이슈로 인한 기대감. 주가 조작 의혹 및 부정적 의견 혼재.</t>
+          <t>정치적 발언 다수. 자사주 소각 기대감 있으나 전반적인 하락세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', 'AI']</t>
+          <t>['정치', '자사주 소각', '주가 방어']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208750</v>
+        <v>16820</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-3.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
-        <v>540</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>1596</v>
+        <v>121</v>
       </c>
       <c r="H10" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K10" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L10" t="n">
-        <v>211000</v>
+        <v>19070</v>
       </c>
       <c r="M10" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N10" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>1143643513500</v>
+        <v>42573495470</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-319000</v>
+        <v>-40000</v>
       </c>
       <c r="S10" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 발언이 주를 이루며, 주가에 대한 객관적인 분석이나 근거는 부족함. 감정적인 비난이 다수.</t>
+          <t>미국 보안주 강세 및 AI 해킹 관련 기사. 주가조작 의혹 제기 및 수급 불안정.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['보안주', 'AI', '주가조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16690</v>
+        <v>16670</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.64%</t>
+          <t>'-3.75%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>12274392810</v>
+        <v>13016800100</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>신저점 경신 및 주가 하락에 대한 불만이 주를 이룸. 주주 환원 정책에 대한 기대감 언급되나 불확실.</t>
+          <t>주주환원정책 발표 가능성 및 외국인 매수 움직임. 반면 신저점 및 하락 추세 지속.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주주환원']</t>
+          <t>['주주환원', '외국인 매수', '신저점']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59100</v>
+        <v>58900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="F12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G12" t="n">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>47859558350</v>
+        <v>52561915700</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>공매도 및 시장 하락에 대한 부정적인 전망이 지배적. 일부 반등에 대한 기대도 있으나 구체적 근거 부족.</t>
+          <t>미국 증시 폭락 영향 및 공매도 관련 우려. 반등 가능성 언급 있으나 전반적 하락세.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도']</t>
+          <t>['공매도', '미국 증시', '반등']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9510</v>
+        <v>9350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.75%</t>
+          <t>'-7.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>25853517220</v>
+        <v>28017630255</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>종목에 대한 부정적인 전망과 함께 야금야금 털고 있다는 의견 존재. 일부 긍정적인 기대도 있으나 불확실.</t>
+          <t>AI 산업통상부 장관 표창 관련 뉴스. 단기 급등 후 조정 및 개미 투자자 매수 유입.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조정']</t>
+          <t>['AI', '수출', '개미 투자자']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_10.xlsx
+++ b/data/trending_integrated_20261023_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4225</v>
+        <v>4230</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.67%</t>
+          <t>'+12.80%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>106781430196</v>
+        <v>110693991076</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60000</v>
+        <v>60300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.30%</t>
+          <t>'+8.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F3" t="n">
         <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>437062622150</v>
+        <v>453624503300</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관 매수세 유입 및 자사주 매입/소각 효과 기대. MSCI 패시브 자금 유입 전망.</t>
+          <t>외인·기관의 대규모 자사주 매입 및 소각 발표, MSCI 패시브 자금 유입 기대감으로 인한 주가 상승 전망. 목표가 12~13만원 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['외인', '자사주 매입', 'MSCI']</t>
+          <t>['자사주 매입', 'MSCI', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8770</v>
+        <v>8720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.04%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H4" t="n">
         <v>5.11</v>
@@ -794,7 +794,7 @@
         <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>5228684085</v>
+        <v>5323356115</v>
       </c>
       <c r="P4" t="n">
         <v>15900</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신풍제약 관련하여 뇌졸중 치료제, 에볼라 치료제 관련 내용 및 특허 언급. 허풍제약이라는 비판적 의견과 함께 단타 매매 및 주포 장난질 의혹 제기. 긍정적 소식에도 불구하고 부정적 전망.</t>
+          <t>글로벌 64개국 특허 확보에도 불구하고 약효 증명 실패로 인한 주가 하락. 주포의 단타 및 장난질 의혹 제기. 미국 에볼라 관련 뉴스로 인한 불확실성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['뇌졸중 치료제', '에볼라', '특허']</t>
+          <t>['특허', '약효 증명', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14510</v>
+        <v>13400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.06</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="H5" t="n">
-        <v>9.890000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14530</v>
+        <v>13340</v>
       </c>
       <c r="K5" t="n">
-        <v>14190</v>
+        <v>12840</v>
       </c>
       <c r="L5" t="n">
-        <v>14610</v>
+        <v>13540</v>
       </c>
       <c r="M5" t="n">
-        <v>13810</v>
+        <v>12530</v>
       </c>
       <c r="N5" t="n">
-        <v>9.949999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="O5" t="n">
-        <v>13920064960</v>
+        <v>32630009035</v>
       </c>
       <c r="P5" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R5" t="n">
-        <v>-17000</v>
+        <v>127000</v>
       </c>
       <c r="S5" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 비난 다수. 주가조작 및 공매도 관련 의혹 제기. 실적 관련 언급 부족.</t>
+          <t>미국 광통신주 급락에도 불구하고 바닥권 탈출 시도. 삼성 인수설 및 외인 매수세 유입으로 반등 기대감 형성. 10월 9990원 목표 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '외인보유률']</t>
+          <t>['광통신주', '삼성 인수설', '외인 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1221000</v>
+        <v>14590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.16%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>513</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>1417</v>
+        <v>94</v>
       </c>
       <c r="H6" t="n">
-        <v>48.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1223000</v>
+        <v>14530</v>
       </c>
       <c r="K6" t="n">
-        <v>1200000</v>
+        <v>14190</v>
       </c>
       <c r="L6" t="n">
-        <v>1235000</v>
+        <v>14710</v>
       </c>
       <c r="M6" t="n">
-        <v>1171000</v>
+        <v>13810</v>
       </c>
       <c r="N6" t="n">
-        <v>48.79</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1667626834500</v>
+        <v>15879747185</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>468000</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-272000</v>
+        <v>-17000</v>
       </c>
       <c r="S6" t="n">
-        <v>79000</v>
+        <v>27000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>목표가 상향 제시 및 기관 매수 방어 움직임. 솔리다임 이슈 완화 기대.</t>
+          <t>주가조작 및 공매도 관련 의혹 제기. 3분기 실적 발표 이후 주가 하락 우려. 외인 보유율 12.41% 유지 희망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['목표가', '기관 매수', '솔리다임']</t>
+          <t>['주가조작', '공매도', '3분기 실적']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13225</v>
+        <v>1215500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-0.61%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>508</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>1431</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>48.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13340</v>
+        <v>1223000</v>
       </c>
       <c r="K7" t="n">
-        <v>12840</v>
+        <v>1200000</v>
       </c>
       <c r="L7" t="n">
-        <v>13310</v>
+        <v>1237000</v>
       </c>
       <c r="M7" t="n">
-        <v>12530</v>
+        <v>1171000</v>
       </c>
       <c r="N7" t="n">
-        <v>3.48</v>
+        <v>48.79</v>
       </c>
       <c r="O7" t="n">
-        <v>27445961110</v>
+        <v>1836940560500</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1640</v>
+        <v>468000</v>
       </c>
       <c r="R7" t="n">
-        <v>127000</v>
+        <v>-272000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신주 급락 영향 및 국내 증시 하방 압력. EUV 반도체 유리기판 특허 관련 언급.</t>
+          <t>솔리다임 관련 악재에도 불구하고 기관 매수세로 방어 시도. 정부의 시장 개입 및 연기금 손실 우려 제기. 목표가 470만원 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', 'EUV', '유리기판']</t>
+          <t>['솔리다임', '기관 매수', '연기금']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7160</v>
+        <v>7170</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.97%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
         <v>38</v>
@@ -1153,7 +1153,7 @@
         <v>7100</v>
       </c>
       <c r="L8" t="n">
-        <v>7210</v>
+        <v>7220</v>
       </c>
       <c r="M8" t="n">
         <v>7010</v>
@@ -1162,7 +1162,7 @@
         <v>25.47</v>
       </c>
       <c r="O8" t="n">
-        <v>6353181855</v>
+        <v>6752913575</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209500</v>
+        <v>17020</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.33%</t>
+          <t>'-1.90%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>536</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>1551</v>
+        <v>125</v>
       </c>
       <c r="H9" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K9" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L9" t="n">
-        <v>211000</v>
+        <v>19070</v>
       </c>
       <c r="M9" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N9" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1202258655750</v>
+        <v>43380986240</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-319000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 발언 다수. 자사주 소각 기대감 있으나 전반적인 하락세.</t>
+          <t>미국 보안주 급등 속 라온시큐어는 부진. AI 보안 이슈 및 고객 계좌 해킹 우려 확산. 시총 2천억대. 안랩 등 보안 대형주와 비교.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치', '자사주 소각', '주가 방어']</t>
+          <t>['AI 보안', '고객 계좌 해킹', '안랩']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16820</v>
+        <v>208000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.05%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>532</v>
       </c>
       <c r="G10" t="n">
-        <v>121</v>
+        <v>1506</v>
       </c>
       <c r="H10" t="n">
-        <v>3.77</v>
+        <v>46.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17350</v>
+        <v>214500</v>
       </c>
       <c r="K10" t="n">
-        <v>18130</v>
+        <v>206000</v>
       </c>
       <c r="L10" t="n">
-        <v>19070</v>
+        <v>211000</v>
       </c>
       <c r="M10" t="n">
-        <v>16530</v>
+        <v>203500</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>42573495470</v>
+        <v>1295739123250</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-40000</v>
+        <v>-319000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 보안주 강세 및 AI 해킹 관련 기사. 주가조작 의혹 제기 및 수급 불안정.</t>
+          <t>정치적 이슈와 맞물려 하락세 지속. 자사주 소각 예정이나 시장 전반의 불안감으로 인한 투자 심리 위축. 목표가 9만 전자 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '주가조작']</t>
+          <t>['정치적 이슈', '자사주 소각', '9만 전자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16670</v>
+        <v>16650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.75%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
         <v>40</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>13016800100</v>
+        <v>13770260605</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58900</v>
+        <v>59100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.38%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G12" t="n">
-        <v>380</v>
+        <v>436</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>52561915700</v>
+        <v>58963214750</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 영향 및 공매도 관련 우려. 반등 가능성 언급 있으나 전반적 하락세.</t>
+          <t>미 증시 폭락과 함께 급락세. 공매도 물량 과다 및 정부의 방어 부재로 인한 추가 하락 우려. 57,000원 이탈 시 위험 경고.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '미국 증시', '반등']</t>
+          <t>['미 증시 폭락', '공매도', '57000원']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9350</v>
+        <v>9320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.33%</t>
+          <t>'-7.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>28017630255</v>
+        <v>29342583390</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261023_10.xlsx
+++ b/data/trending_integrated_20261023_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4230</v>
+        <v>4225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.80%</t>
+          <t>'+12.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G2" t="n">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>110693991076</v>
+        <v>113413762291</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60300</v>
+        <v>60900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.84%</t>
+          <t>'+9.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F3" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G3" t="n">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>453624503300</v>
+        <v>465039626450</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8720</v>
+        <v>13520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+1.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="H4" t="n">
-        <v>5.11</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8680</v>
+        <v>13340</v>
       </c>
       <c r="K4" t="n">
-        <v>9410</v>
+        <v>12840</v>
       </c>
       <c r="L4" t="n">
-        <v>9460</v>
+        <v>13540</v>
       </c>
       <c r="M4" t="n">
-        <v>8640</v>
+        <v>12530</v>
       </c>
       <c r="N4" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="O4" t="n">
-        <v>5323356115</v>
+        <v>35233523240</v>
       </c>
       <c r="P4" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>6310</v>
+        <v>1640</v>
       </c>
       <c r="R4" t="n">
-        <v>-186000</v>
+        <v>127000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>글로벌 64개국 특허 확보에도 불구하고 약효 증명 실패로 인한 주가 하락. 주포의 단타 및 장난질 의혹 제기. 미국 에볼라 관련 뉴스로 인한 불확실성.</t>
+          <t>EUV 반도체 유리기판 기술성에 대한 AI 분석 언급 및 외인 매수세 유입. 미장 광통신주와 비교하며 바닥 탈출 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특허', '약효 증명', '주포']</t>
+          <t>['유리기판', 'AI분석', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13400</v>
+        <v>14650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.83%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="H5" t="n">
-        <v>2.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13340</v>
+        <v>14530</v>
       </c>
       <c r="K5" t="n">
-        <v>12840</v>
+        <v>14190</v>
       </c>
       <c r="L5" t="n">
-        <v>13540</v>
+        <v>14710</v>
       </c>
       <c r="M5" t="n">
-        <v>12530</v>
+        <v>13810</v>
       </c>
       <c r="N5" t="n">
-        <v>3.48</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>32630009035</v>
+        <v>16653325535</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>1640</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>127000</v>
+        <v>-17000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 광통신주 급락에도 불구하고 바닥권 탈출 시도. 삼성 인수설 및 외인 매수세 유입으로 반등 기대감 형성. 10월 9990원 목표 제시.</t>
+          <t>주가 조작 의혹 제기와 함께 대차 해지 독려. 실적 발표 및 외인 보유율 관리에 대한 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신주', '삼성 인수설', '외인 매수']</t>
+          <t>['주가조작', '대차해지', '외인보유율']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14590</v>
+        <v>1231000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.65%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>502</v>
       </c>
       <c r="G6" t="n">
-        <v>94</v>
+        <v>1424</v>
       </c>
       <c r="H6" t="n">
-        <v>9.890000000000001</v>
+        <v>48.77</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14530</v>
+        <v>1223000</v>
       </c>
       <c r="K6" t="n">
-        <v>14190</v>
+        <v>1200000</v>
       </c>
       <c r="L6" t="n">
-        <v>14710</v>
+        <v>1237000</v>
       </c>
       <c r="M6" t="n">
-        <v>13810</v>
+        <v>1171000</v>
       </c>
       <c r="N6" t="n">
-        <v>9.949999999999999</v>
+        <v>48.79</v>
       </c>
       <c r="O6" t="n">
-        <v>15879747185</v>
+        <v>1926695170500</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>468000</v>
       </c>
       <c r="R6" t="n">
-        <v>-17000</v>
+        <v>-272000</v>
       </c>
       <c r="S6" t="n">
-        <v>27000</v>
+        <v>79000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가조작 및 공매도 관련 의혹 제기. 3분기 실적 발표 이후 주가 하락 우려. 외인 보유율 12.41% 유지 희망.</t>
+          <t>주주환원 발표 기대감 속 정부의 시장 개입에 대한 우려가 혼재. 기관 매수세 방어 정황.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '3분기 실적']</t>
+          <t>['주주환원', '기관매수', '시장개입']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1215500</v>
+        <v>8720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="F7" t="n">
-        <v>508</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>1431</v>
+        <v>163</v>
       </c>
       <c r="H7" t="n">
-        <v>48.77</v>
+        <v>5.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1223000</v>
+        <v>8680</v>
       </c>
       <c r="K7" t="n">
-        <v>1200000</v>
+        <v>9410</v>
       </c>
       <c r="L7" t="n">
-        <v>1237000</v>
+        <v>9460</v>
       </c>
       <c r="M7" t="n">
-        <v>1171000</v>
+        <v>8640</v>
       </c>
       <c r="N7" t="n">
-        <v>48.79</v>
+        <v>5.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1836940560500</v>
+        <v>5352214540</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>15900</v>
       </c>
       <c r="Q7" t="n">
-        <v>468000</v>
+        <v>6310</v>
       </c>
       <c r="R7" t="n">
-        <v>-272000</v>
+        <v>-186000</v>
       </c>
       <c r="S7" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>솔리다임 관련 악재에도 불구하고 기관 매수세로 방어 시도. 정부의 시장 개입 및 연기금 손실 우려 제기. 목표가 470만원 언급.</t>
+          <t>신약 개발 관련 특허 및 3상 성공 가능성 언급에도 불구하고 약효 증명 미흡에 따른 주가 하락 우려. 단기 매매 차익에 대한 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['솔리다임', '기관 매수', '연기금']</t>
+          <t>['신약개발', '특허', '주가하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7170</v>
+        <v>7200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
         <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H8" t="n">
         <v>25.42</v>
@@ -1162,7 +1162,7 @@
         <v>25.47</v>
       </c>
       <c r="O8" t="n">
-        <v>6752913575</v>
+        <v>7003969135</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17020</v>
+        <v>210750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.90%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>532</v>
       </c>
       <c r="G9" t="n">
-        <v>125</v>
+        <v>1525</v>
       </c>
       <c r="H9" t="n">
-        <v>3.77</v>
+        <v>46.13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17350</v>
+        <v>214500</v>
       </c>
       <c r="K9" t="n">
-        <v>18130</v>
+        <v>206000</v>
       </c>
       <c r="L9" t="n">
-        <v>19070</v>
+        <v>211000</v>
       </c>
       <c r="M9" t="n">
-        <v>16530</v>
+        <v>203500</v>
       </c>
       <c r="N9" t="n">
-        <v>3.29</v>
+        <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>43380986240</v>
+        <v>1364438576000</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-319000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 보안주 급등 속 라온시큐어는 부진. AI 보안 이슈 및 고객 계좌 해킹 우려 확산. 시총 2천억대. 안랩 등 보안 대형주와 비교.</t>
+          <t>정치적 이슈와 맞물려 하락세 지속. 자사주 소각 예정이나 시장 전반의 불안감으로 인한 투자 심리 위축. 목표가 9만 전자 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI 보안', '고객 계좌 해킹', '안랩']</t>
+          <t>['정치적 이슈', '자사주 소각', '9만 전자']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>208000</v>
+        <v>16920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>532</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>1506</v>
+        <v>125</v>
       </c>
       <c r="H10" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K10" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L10" t="n">
-        <v>211000</v>
+        <v>19070</v>
       </c>
       <c r="M10" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N10" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O10" t="n">
-        <v>1295739123250</v>
+        <v>43828926610</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-319000</v>
+        <v>-40000</v>
       </c>
       <c r="S10" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 하락세 지속. 자사주 소각 예정이나 시장 전반의 불안감으로 인한 투자 심리 위축. 목표가 9만 전자 언급.</t>
+          <t>미국 보안주 급등 속 라온시큐어는 부진. AI 보안 이슈 및 고객 계좌 해킹 우려 확산. 시총 2천억대. 안랩 등 보안 대형주와 비교.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '자사주 소각', '9만 전자']</t>
+          <t>['AI 보안', '고객 계좌 해킹', '안랩']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16650</v>
+        <v>59500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-3.41%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>161</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="G11" t="n">
-        <v>106</v>
+        <v>448</v>
       </c>
       <c r="H11" t="n">
-        <v>27.89</v>
+        <v>22.25</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17320</v>
+        <v>61600</v>
       </c>
       <c r="K11" t="n">
-        <v>16810</v>
+        <v>59600</v>
       </c>
       <c r="L11" t="n">
-        <v>16850</v>
+        <v>60000</v>
       </c>
       <c r="M11" t="n">
-        <v>16450</v>
+        <v>57700</v>
       </c>
       <c r="N11" t="n">
-        <v>27.87</v>
+        <v>22.26</v>
       </c>
       <c r="O11" t="n">
-        <v>13770260605</v>
+        <v>62730804500</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>16450</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-46000</v>
+        <v>-25000</v>
       </c>
       <c r="S11" t="n">
-        <v>11000</v>
+        <v>-69000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주주환원정책 발표 가능성 및 외국인 매수 움직임. 반면 신저점 및 하락 추세 지속.</t>
+          <t>미국 증시 폭락에 따른 하락 전망 및 공매도에 대한 강한 불만 표출. 정부 정책에 대한 비판.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주주환원', '외국인 매수', '신저점']</t>
+          <t>['공매도', '증시폭락', '정부정책']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59100</v>
+        <v>16730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-3.41%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>436</v>
+        <v>127</v>
       </c>
       <c r="H12" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>61600</v>
+        <v>17320</v>
       </c>
       <c r="K12" t="n">
-        <v>59600</v>
+        <v>16810</v>
       </c>
       <c r="L12" t="n">
-        <v>60000</v>
+        <v>16850</v>
       </c>
       <c r="M12" t="n">
-        <v>57700</v>
+        <v>16450</v>
       </c>
       <c r="N12" t="n">
-        <v>22.26</v>
+        <v>27.87</v>
       </c>
       <c r="O12" t="n">
-        <v>58963214750</v>
+        <v>14463213005</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>16450</v>
       </c>
       <c r="R12" t="n">
-        <v>-25000</v>
+        <v>-46000</v>
       </c>
       <c r="S12" t="n">
-        <v>-69000</v>
+        <v>11000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미 증시 폭락과 함께 급락세. 공매도 물량 과다 및 정부의 방어 부재로 인한 추가 하락 우려. 57,000원 이탈 시 위험 경고.</t>
+          <t>주주환원 정책 발표 가능성 언급 속 신저점 및 하락 추세에 대한 우려. 조선업 업황에 대한 회의론.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미 증시 폭락', '공매도', '57000원']</t>
+          <t>['주주환원', '신저점', '조선업']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9320</v>
+        <v>9340</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.63%</t>
+          <t>'-7.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1616,13 +1616,13 @@
         <v>10060</v>
       </c>
       <c r="M13" t="n">
-        <v>9280</v>
+        <v>9210</v>
       </c>
       <c r="N13" t="n">
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>29342583390</v>
+        <v>30478306680</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AI 산업통상부 장관 표창 관련 뉴스. 단기 급등 후 조정 및 개미 투자자 매수 유입.</t>
+          <t>조정 및 횡보 예상과 함께 투자 주의 해제 가능성 언급. 단기 급등 및 하락 가능성에 대한 상반된 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI', '수출', '개미 투자자']</t>
+          <t>['조정', '횡보', '투자주의']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_10.xlsx
+++ b/data/trending_integrated_20261023_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4225</v>
+        <v>4360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.67%</t>
+          <t>'+16.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="F2" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>113413762291</v>
+        <v>118618912264</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60900</v>
+        <v>60400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.93%</t>
+          <t>'+9.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="F3" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G3" t="n">
-        <v>679</v>
+        <v>738</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -693,7 +693,7 @@
         <v>56300</v>
       </c>
       <c r="L3" t="n">
-        <v>60900</v>
+        <v>61000</v>
       </c>
       <c r="M3" t="n">
         <v>56200</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>465039626450</v>
+        <v>484167453350</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관의 대규모 자사주 매입 및 소각 발표, MSCI 패시브 자금 유입 기대감으로 인한 주가 상승 전망. 목표가 12~13만원 제시.</t>
+          <t>외인·기관의 삼성E&amp;A 대규모 매수세 유입, MSCI 패시브 자금 유입 및 자사주 매입·소각 공시 기반 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI', '목표가']</t>
+          <t>[' MSCI', '자사주 매입', '패시브 자금']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13520</v>
+        <v>8800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.35%</t>
+          <t>'+1.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>5.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13340</v>
+        <v>8680</v>
       </c>
       <c r="K4" t="n">
-        <v>12840</v>
+        <v>9410</v>
       </c>
       <c r="L4" t="n">
-        <v>13540</v>
+        <v>9460</v>
       </c>
       <c r="M4" t="n">
-        <v>12530</v>
+        <v>8640</v>
       </c>
       <c r="N4" t="n">
-        <v>3.48</v>
+        <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>35233523240</v>
+        <v>5566960080</v>
       </c>
       <c r="P4" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q4" t="n">
-        <v>1640</v>
+        <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>127000</v>
+        <v>-186000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>EUV 반도체 유리기판 기술성에 대한 AI 분석 언급 및 외인 매수세 유입. 미장 광통신주와 비교하며 바닥 탈출 기대.</t>
+          <t>신약 개발 관련 특허 및 3상 성공 가능성 언급에도 불구하고 약효 증명 미흡에 따른 주가 하락 우려. 단기 매매 차익에 대한 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유리기판', 'AI분석', '외인매수']</t>
+          <t>['신약개발', '특허', '주가하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14650</v>
+        <v>13390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.83%</t>
+          <t>'+0.37%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.06</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="H5" t="n">
-        <v>9.890000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14530</v>
+        <v>13340</v>
       </c>
       <c r="K5" t="n">
-        <v>14190</v>
+        <v>12840</v>
       </c>
       <c r="L5" t="n">
-        <v>14710</v>
+        <v>13700</v>
       </c>
       <c r="M5" t="n">
-        <v>13810</v>
+        <v>12530</v>
       </c>
       <c r="N5" t="n">
-        <v>9.949999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="O5" t="n">
-        <v>16653325535</v>
+        <v>41574385695</v>
       </c>
       <c r="P5" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R5" t="n">
-        <v>-17000</v>
+        <v>127000</v>
       </c>
       <c r="S5" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기와 함께 대차 해지 독려. 실적 발표 및 외인 보유율 관리에 대한 언급.</t>
+          <t>EUV 유리기판 기술력에 대한 기대감 및 외인 순매수 유입, 삼성 인수설 등 호재 기반 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가조작', '대차해지', '외인보유율']</t>
+          <t>['EUV 유리기판', '기술력', '삼성 인수설']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1231000</v>
+        <v>14520</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.65%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>502</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>1424</v>
+        <v>95</v>
       </c>
       <c r="H6" t="n">
-        <v>48.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1223000</v>
+        <v>14530</v>
       </c>
       <c r="K6" t="n">
-        <v>1200000</v>
+        <v>14190</v>
       </c>
       <c r="L6" t="n">
-        <v>1237000</v>
+        <v>14710</v>
       </c>
       <c r="M6" t="n">
-        <v>1171000</v>
+        <v>13810</v>
       </c>
       <c r="N6" t="n">
-        <v>48.79</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1926695170500</v>
+        <v>17737513470</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>468000</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-272000</v>
+        <v>-17000</v>
       </c>
       <c r="S6" t="n">
-        <v>79000</v>
+        <v>27000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주주환원 발표 기대감 속 정부의 시장 개입에 대한 우려가 혼재. 기관 매수세 방어 정황.</t>
+          <t>실적 발표 이후 주가 하락세 지속, 공매도 및 주가 조작 의혹 제기, 대차 해지 동참 요구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주주환원', '기관매수', '시장개입']</t>
+          <t>['실적 발표', '공매도', '주가 조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8720</v>
+        <v>1217000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'-0.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>496</v>
       </c>
       <c r="G7" t="n">
-        <v>163</v>
+        <v>1339</v>
       </c>
       <c r="H7" t="n">
-        <v>5.11</v>
+        <v>48.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8680</v>
+        <v>1223000</v>
       </c>
       <c r="K7" t="n">
-        <v>9410</v>
+        <v>1200000</v>
       </c>
       <c r="L7" t="n">
-        <v>9460</v>
+        <v>1237000</v>
       </c>
       <c r="M7" t="n">
-        <v>8640</v>
+        <v>1171000</v>
       </c>
       <c r="N7" t="n">
-        <v>5.15</v>
+        <v>48.79</v>
       </c>
       <c r="O7" t="n">
-        <v>5352214540</v>
+        <v>2023505387500</v>
       </c>
       <c r="P7" t="n">
-        <v>15900</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>6310</v>
+        <v>468000</v>
       </c>
       <c r="R7" t="n">
-        <v>-186000</v>
+        <v>-272000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신약 개발 관련 특허 및 3상 성공 가능성 언급에도 불구하고 약효 증명 미흡에 따른 주가 하락 우려. 단기 매매 차익에 대한 언급.</t>
+          <t>반도체 업황 악화 우려 속 연기금 손실 및 주주 환원 발표 기대감 혼재, 주가 부양 정책 필요성 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신약개발', '특허', '주가하락']</t>
+          <t>['반도체 업황', '연기금', '주주 환원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7200</v>
+        <v>7150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.41%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="H8" t="n">
         <v>25.42</v>
@@ -1162,7 +1162,7 @@
         <v>25.47</v>
       </c>
       <c r="O8" t="n">
-        <v>7003969135</v>
+        <v>7298615445</v>
       </c>
       <c r="P8" t="n">
         <v>17950</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>분기 순이익 증가 및 재무 상태 개선 등 긍정적인 실적 발표. FLiPP 개발 성공에 대한 기대감 존재.</t>
+          <t>컨센서스 상회하는 호실적 발표 및 재무 상태 개선, 신사업 모멘텀 및 배당 기대감으로 인한 주가 반등 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['순이익', 'FLiPP']</t>
+          <t>['호실적', '신사업', '배당']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210750</v>
+        <v>16910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-2.54%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="F9" t="n">
-        <v>532</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>1525</v>
+        <v>133</v>
       </c>
       <c r="H9" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K9" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L9" t="n">
-        <v>211000</v>
+        <v>19070</v>
       </c>
       <c r="M9" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N9" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1364438576000</v>
+        <v>44337515255</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-319000</v>
+        <v>-40000</v>
       </c>
       <c r="S9" t="n">
-        <v>113000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 하락세 지속. 자사주 소각 예정이나 시장 전반의 불안감으로 인한 투자 심리 위축. 목표가 9만 전자 언급.</t>
+          <t>미국 보안주 강세와 달리 국내 주가 부진, 주가 조작 의혹 및 수급 불안정으로 인한 하락 압력.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '자사주 소각', '9만 전자']</t>
+          <t>['보안주', '주가 조작', '수급']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16920</v>
+        <v>208250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>533</v>
       </c>
       <c r="G10" t="n">
-        <v>125</v>
+        <v>1365</v>
       </c>
       <c r="H10" t="n">
-        <v>3.77</v>
+        <v>46.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17350</v>
+        <v>214500</v>
       </c>
       <c r="K10" t="n">
-        <v>18130</v>
+        <v>206000</v>
       </c>
       <c r="L10" t="n">
-        <v>19070</v>
+        <v>212000</v>
       </c>
       <c r="M10" t="n">
-        <v>16530</v>
+        <v>203500</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>43828926610</v>
+        <v>1451781911000</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-40000</v>
+        <v>-319000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 보안주 급등 속 라온시큐어는 부진. AI 보안 이슈 및 고객 계좌 해킹 우려 확산. 시총 2천억대. 안랩 등 보안 대형주와 비교.</t>
+          <t>정치적 이슈로 인한 부정적 여론 확산, 실적 부진에 대한 실망감으로 인한 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 보안', '고객 계좌 해킹', '안랩']</t>
+          <t>['정치 이슈', '실적 부진', '주가 하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59500</v>
+        <v>16600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.41%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>448</v>
+        <v>140</v>
       </c>
       <c r="H11" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>61600</v>
+        <v>17320</v>
       </c>
       <c r="K11" t="n">
-        <v>59600</v>
+        <v>16810</v>
       </c>
       <c r="L11" t="n">
-        <v>60000</v>
+        <v>16850</v>
       </c>
       <c r="M11" t="n">
-        <v>57700</v>
+        <v>16450</v>
       </c>
       <c r="N11" t="n">
-        <v>22.26</v>
+        <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>62730804500</v>
+        <v>15746902315</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>16450</v>
       </c>
       <c r="R11" t="n">
-        <v>-25000</v>
+        <v>-46000</v>
       </c>
       <c r="S11" t="n">
-        <v>-69000</v>
+        <v>11000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 폭락에 따른 하락 전망 및 공매도에 대한 강한 불만 표출. 정부 정책에 대한 비판.</t>
+          <t>조선업종 전반의 하락세 속 주가 부진 지속, 주주환원 정책 및 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '증시폭락', '정부정책']</t>
+          <t>['조선업', '주주환원', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16730</v>
+        <v>58600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.41%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="G12" t="n">
-        <v>127</v>
+        <v>469</v>
       </c>
       <c r="H12" t="n">
-        <v>27.89</v>
+        <v>22.25</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17320</v>
+        <v>61600</v>
       </c>
       <c r="K12" t="n">
-        <v>16810</v>
+        <v>59600</v>
       </c>
       <c r="L12" t="n">
-        <v>16850</v>
+        <v>60000</v>
       </c>
       <c r="M12" t="n">
-        <v>16450</v>
+        <v>57700</v>
       </c>
       <c r="N12" t="n">
-        <v>27.87</v>
+        <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>14463213005</v>
+        <v>65798927750</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>16450</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-46000</v>
+        <v>-25000</v>
       </c>
       <c r="S12" t="n">
-        <v>11000</v>
+        <v>-69000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주주환원 정책 발표 가능성 언급 속 신저점 및 하락 추세에 대한 우려. 조선업 업황에 대한 회의론.</t>
+          <t>미 증시 폭락 영향 및 공매도 물량 부담으로 인한 주가 하락세 지속, 정부 정책 및 무능 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주주환원', '신저점', '조선업']</t>
+          <t>['미 증시', '공매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9340</v>
+        <v>9270</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-7.43%</t>
+          <t>'-8.13%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" t="n">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>30478306680</v>
+        <v>31651523930</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>조정 및 횡보 예상과 함께 투자 주의 해제 가능성 언급. 단기 급등 및 하락 가능성에 대한 상반된 전망.</t>
+          <t>악화된 수급 및 기술적 지표 하락으로 인한 주가 급락 우려, 투자 주의 종목 지정 가능성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조정', '횡보', '투자주의']</t>
+          <t>['수급', '기술적 지표', '급락']</t>
         </is>
       </c>
       <c r="X13" t="n">
